--- a/survey_templates/033_holistic_health_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/033_holistic_health_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'good'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'Good'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'fair'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'Fair'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'poor'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'Poor'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'yoga'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'Yoga'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'meditation'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Meditation'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'mindfulness'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Mindfulness'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'high'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'High'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'medium'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'Medium'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'low'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'Low'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'financial'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'Financial'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'family'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'Family'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'work'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'Work'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'health'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'Health'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'white'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'White'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'black'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Black'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'high_school'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'High School'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'some_college'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'Some College'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_"bachelor's"}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': "Bachelor's"}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_"master's"}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': "Master's"}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'doctoral'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'Doctoral'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'student'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'Student'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'working'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': 'Working'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'unemployed'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'Unemployed'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'Other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'full-time'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'Full-Time'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'part-time'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'Part-Time'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'unemployed'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'Unemployed'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'married'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'Married'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'single'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': 'Single'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_'divorced'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': 'Divorced'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_'widowed'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': 'Widowed'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option':_'employer'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option': 'Employer'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option':_'private_insurance'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option': 'Private Insurance'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1686,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option':_'medicaid'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option': 'Medicaid'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option':_'medicare'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option': 'Medicare'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'option':_'diabetes'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'option': 'Diabetes'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'option':_'high_blood_pressure'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'option': 'High Blood Pressure'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'option':_'high_cholesterol'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'option': 'High Cholesterol'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1856,12 +1856,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option':_'7-8_hours'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option': '7-8 Hours'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'option':_'8-10_hours'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'option': '8-10 Hours'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'option':_'10_hours_or_more'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'option': '10 Hours or more'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1924,12 +1924,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option':_false}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option': False}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
